--- a/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
+++ b/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:27:28+00:00</t>
+    <t>2025-03-11T13:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
+++ b/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:28:38+00:00</t>
+    <t>2025-03-11T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
+++ b/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:29:42+00:00</t>
+    <t>2025-03-17T15:05:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
+++ b/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-17T15:05:50+00:00</t>
+    <t>2025-03-18T10:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
+++ b/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T10:04:30+00:00</t>
+    <t>2025-03-20T11:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
+++ b/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T11:13:27+00:00</t>
+    <t>2025-03-20T15:00:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
+++ b/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T15:00:12+00:00</t>
+    <t>2025-03-24T10:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
+++ b/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T10:58:19+00:00</t>
+    <t>2025-03-24T11:01:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
+++ b/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:08+00:00</t>
+    <t>2025-03-24T12:21:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
+++ b/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T12:21:29+00:00</t>
+    <t>2025-03-26T10:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
+++ b/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-26T10:25:04+00:00</t>
+    <t>2025-04-17T09:39:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
+++ b/branches/sandbox/CodeSystem-PSSRatingTypes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-17T09:39:14+00:00</t>
+    <t>2025-04-17T11:28:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
